--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16778,27 +16778,27 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -16808,52 +16808,52 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -16863,52 +16863,52 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I300" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -16918,25 +16918,25 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -17371,12 +17371,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -17426,12 +17426,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -17481,12 +17481,232 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>2026/05/28 15:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>13</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
           <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>13</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>13</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
         <is>
           <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>5</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>

--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K317"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2428,330 +2428,330 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17U1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VenturePro 17 AI A2HVEG</t>
+          <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2025/07/12</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025/04/15</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>-88</v>
+        <v>7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/07/03 08:16:45</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17U1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VenturePro 17 AI A2HVEG</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025/07/12</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2025/04/15</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>-88</v>
+        <v>7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/07/03 08:16:45</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/07/03 08:16:45</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/07/03 08:16:45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>17U1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>VenturePro 17 AI A2HVEG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2025/07/12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-2</v>
+        <v>-88</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>17U1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>VenturePro 17 AI A2HVEG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2025/07/12</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>-2</v>
+        <v>-88</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4181,89 +4181,89 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>BTO未開</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4273,37 +4273,42 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>14</v>
+        <v>-2</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4313,7 +4318,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4323,75 +4328,80 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>BTO未開</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>14</v>
+        <v>-2</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4456,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4506,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4561,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4611,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4666,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4716,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4771,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4821,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4833,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Raider A18 HX A9WIG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4843,12 +4853,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4857,16 +4867,16 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>-26</v>
+        <v>-14</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>業務8/6通知開BTO</t>
+          <t>BTO未開</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4888,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Raider A18 HX A9WJG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4903,20 +4913,20 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2025/03/17</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -4928,17 +4938,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WHG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4948,25 +4958,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2025/04/02</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025/03/27</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>-6</v>
+        <v>-14</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>BTO未開</t>
+        </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5031,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5086,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5136,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5186,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5221,227 +5236,212 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM</t>
+          <t>Raider A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2025/03/26</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>業務8/6通知開BTO</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
+          <t>Raider A18 HX A9WJG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/03/17</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/26</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>follow 12XE</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM</t>
+          <t>Vector A18 HX A9WHG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
-        </is>
+        <v>-6</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>follow 12XE</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -6321,24 +6321,24 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6348,52 +6348,52 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6403,52 +6403,52 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>follow 12XE</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6458,52 +6458,52 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6513,35 +6513,35 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>follow 12XE</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -6921,12 +6921,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -7073,42 +7073,42 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）  3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026/06/18 13:35:09</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7118,52 +7118,52 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026/06/16 08:16:09</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7173,52 +7173,52 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026/06/16 08:19:44</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7228,52 +7228,52 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026/06/16 08:22:24</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7283,35 +7283,35 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>-42</v>
+        <v>2</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）  3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026/06/16 08:28:05</t>
+          <t>2026/06/18 13:35:09</t>
         </is>
       </c>
     </row>
@@ -7366,29 +7366,29 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026/06/16 08:33:57</t>
+          <t>2026/06/16 08:16:09</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7398,52 +7398,52 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:19:44</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7453,52 +7453,52 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:22:24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7508,52 +7508,52 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>-42</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:28:05</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7563,30 +7563,30 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:33:57</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8026,227 +8026,227 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9358,17 +9358,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9378,30 +9378,30 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9498,11 +9498,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9598,25 +9598,25 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9663,20 +9663,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>-12</v>
+        <v>23</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9688,17 +9688,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9713,16 +9713,16 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>23</v>
+        <v>-15</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9743,17 +9743,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9768,16 +9768,16 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9873,25 +9873,25 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -9903,12 +9903,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9918,17 +9918,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9938,70 +9938,70 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>-12</v>
+        <v>23</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10013,127 +10013,127 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10143,52 +10143,52 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10198,255 +10198,255 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026/06/22 16:04:37</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>263</v>
+        <v>-1</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/06/22 16:04:37</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -10886,24 +10886,24 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10913,52 +10913,52 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10968,52 +10968,52 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11023,90 +11023,90 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12206,19 +12206,19 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12228,52 +12228,52 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>-29</v>
+        <v>-352</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12298,107 +12298,107 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="I217" t="n">
-        <v>-29</v>
+        <v>-352</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -12438,12 +12438,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -12458,21 +12458,21 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I220" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -12513,25 +12513,25 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12568,25 +12568,25 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I222" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12628,16 +12628,16 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -12658,17 +12658,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12678,21 +12678,21 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -12713,12 +12713,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -12733,25 +12733,25 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -12768,17 +12768,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -12788,25 +12788,25 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -12912,7 +12912,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -12933,17 +12933,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -12963,11 +12963,11 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -12988,12 +12988,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13043,12 +13043,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -13063,21 +13063,21 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13118,25 +13118,25 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13173,25 +13173,25 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -13233,16 +13233,16 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I234" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13263,17 +13263,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13283,21 +13283,21 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I235" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13318,12 +13318,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -13338,25 +13338,25 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -13373,17 +13373,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13393,25 +13393,25 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I237" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13538,17 +13538,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -13568,11 +13568,11 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13648,12 +13648,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -13668,21 +13668,21 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I242" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -13723,25 +13723,25 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I243" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13778,25 +13778,25 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I244" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -13813,12 +13813,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -13838,16 +13838,16 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I245" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -13868,17 +13868,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13888,21 +13888,21 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I246" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -13923,12 +13923,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -13943,25 +13943,25 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I247" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -13978,17 +13978,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13998,25 +13998,25 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -14173,11 +14173,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14198,12 +14198,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14253,12 +14253,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -14273,21 +14273,21 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14328,25 +14328,25 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14383,25 +14383,25 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -14418,12 +14418,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -14443,16 +14443,16 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I256" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -14473,17 +14473,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14493,21 +14493,21 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I257" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -14548,25 +14548,25 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -14583,17 +14583,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -14603,25 +14603,25 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -14658,12 +14658,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14748,17 +14748,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -14778,11 +14778,11 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14803,12 +14803,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14858,12 +14858,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -14878,21 +14878,21 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I264" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14933,25 +14933,25 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I265" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14988,25 +14988,25 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -15048,16 +15048,16 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I267" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -15078,17 +15078,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15098,21 +15098,21 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I268" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15133,12 +15133,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -15153,25 +15153,25 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15208,25 +15208,25 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15263,12 +15263,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -15332,7 +15332,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15353,17 +15353,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -15383,11 +15383,11 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15408,12 +15408,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -15483,21 +15483,21 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15538,25 +15538,25 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15593,25 +15593,25 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -15653,16 +15653,16 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I278" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -15683,17 +15683,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -15703,21 +15703,21 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -15738,12 +15738,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -15758,25 +15758,25 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -15793,17 +15793,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15813,25 +15813,25 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -15848,12 +15848,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -15873,16 +15873,16 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>-28</v>
+        <v>-67</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -15903,12 +15903,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -15923,21 +15923,21 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I283" t="n">
-        <v>28</v>
+        <v>-67</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -15983,7 +15983,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>-28</v>
+        <v>59</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16033,21 +16033,21 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I285" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -16088,21 +16088,21 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I286" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16178,12 +16178,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -16198,21 +16198,21 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I288" t="n">
-        <v>2</v>
+        <v>-28</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16233,12 +16233,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -16258,25 +16258,25 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I289" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16313,16 +16313,16 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I290" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16398,17 +16398,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16423,16 +16423,16 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I292" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16491,12 +16491,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16546,12 +16546,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16563,17 +16563,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16588,16 +16588,16 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I295" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16673,17 +16673,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -16698,16 +16698,16 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I297" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -16766,12 +16766,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16821,12 +16821,12 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16838,17 +16838,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16863,16 +16863,16 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I300" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -16893,17 +16893,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16918,16 +16918,16 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16973,12 +16973,12 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I302" t="n">
@@ -16986,12 +16986,12 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I303" t="n">
@@ -17041,39 +17041,39 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -17092,43 +17092,43 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -17138,52 +17138,52 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I305" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -17193,52 +17193,52 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I306" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -17248,25 +17248,25 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I307" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -17646,12 +17646,12 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -17701,12 +17701,12 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -17756,12 +17756,12 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -17798,23 +17798,243 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
+      <c r="I317" t="n">
+        <v>13</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>2026/05/28 15:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I318" t="n">
+        <v>13</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I319" t="n">
+        <v>13</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I320" t="n">
+        <v>13</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
         <is>
           <t>2026/07/13</t>
         </is>
       </c>
-      <c r="I317" t="n">
+      <c r="I321" t="n">
         <v>5</v>
       </c>
-      <c r="J317" t="inlineStr">
+      <c r="J321" t="inlineStr">
         <is>
           <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
+      <c r="K321" t="inlineStr">
         <is>
           <t>2026/06/26 13:22:28</t>
         </is>

--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/14),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026/07/03 08:16:45</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/14),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026/07/03 08:16:45</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/14),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026/07/03 08:16:45</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 延至7/10(Delay 3W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計僅延後 1 週至 9/7 (先前已由9 月底提前至8/31,現又延至9/7),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/14),後續將依實際測試結果滾動式調整時程。 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026/07/03 08:16:45</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -7318,17 +7318,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Prestige N16 Spark</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7338,52 +7338,52 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026/06/16 08:16:09</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7393,35 +7393,35 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026/06/16 08:19:44</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026/06/16 08:22:24</t>
+          <t>2026/06/16 08:16:09</t>
         </is>
       </c>
     </row>
@@ -7513,16 +7513,16 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
           <t>2026/10/26</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>-42</v>
+        <v>42</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026/06/16 08:28:05</t>
+          <t>2026/06/16 08:19:44</t>
         </is>
       </c>
     </row>
@@ -7586,29 +7586,29 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026/06/16 08:33:57</t>
+          <t>2026/06/16 08:22:24</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7618,52 +7618,52 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>-42</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:28:05</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7673,30 +7673,30 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:33:57</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8253,110 +8253,110 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8398,11 +8398,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8618,11 +8618,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8838,11 +8838,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9058,11 +9058,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9278,11 +9278,11 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9498,11 +9498,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9578,12 +9578,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9598,30 +9598,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9688,17 +9688,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9708,25 +9708,25 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -9798,17 +9798,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8</v>
+        <v>-15</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9873,30 +9873,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -9963,17 +9963,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9983,25 +9983,25 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -10073,17 +10073,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10098,16 +10098,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>8</v>
+        <v>-15</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -10123,12 +10123,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10138,52 +10138,52 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10193,35 +10193,35 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10233,17 +10233,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10253,52 +10253,52 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10308,35 +10308,35 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -10428,135 +10428,135 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
           <t>2026/06/19</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026/06/22 16:04:37</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>263</v>
+        <v>-1</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/22 16:04:37</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -11106,24 +11106,24 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11133,52 +11133,52 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11188,35 +11188,35 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11228,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11248,25 +11248,25 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11283,17 +11283,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11303,25 +11303,25 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11338,12 +11338,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11358,30 +11358,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11393,17 +11393,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11413,30 +11413,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11448,12 +11448,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11468,25 +11468,25 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -11503,17 +11503,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11523,25 +11523,25 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11578,30 +11578,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11613,17 +11613,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11633,30 +11633,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11688,25 +11688,25 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -11723,17 +11723,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11743,25 +11743,25 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11798,30 +11798,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11833,17 +11833,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11853,30 +11853,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11888,12 +11888,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11908,25 +11908,25 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -11943,17 +11943,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11963,25 +11963,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -12018,30 +12018,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12053,17 +12053,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12073,30 +12073,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -12128,25 +12128,25 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12163,17 +12163,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12183,25 +12183,25 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -12238,30 +12238,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I216" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12273,17 +12273,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12293,30 +12293,30 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I217" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -12348,25 +12348,25 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12403,25 +12403,25 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -12433,110 +12433,110 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -12568,21 +12568,21 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -12603,17 +12603,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12623,21 +12623,21 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -12658,17 +12658,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12678,21 +12678,21 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -12713,12 +12713,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -12733,25 +12733,25 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -12768,17 +12768,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -12788,25 +12788,25 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12843,25 +12843,25 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12898,25 +12898,25 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -12933,12 +12933,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -12958,16 +12958,16 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -12988,17 +12988,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13013,16 +13013,16 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -13043,12 +13043,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -13063,21 +13063,21 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13098,17 +13098,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13118,21 +13118,21 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13153,7 +13153,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13173,21 +13173,21 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -13208,17 +13208,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13228,21 +13228,21 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13263,17 +13263,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13283,21 +13283,21 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13318,12 +13318,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -13338,25 +13338,25 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -13373,17 +13373,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -13393,25 +13393,25 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13448,25 +13448,25 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13503,25 +13503,25 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -13563,16 +13563,16 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -13593,17 +13593,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13618,16 +13618,16 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -13648,12 +13648,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -13668,21 +13668,21 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I242" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13703,17 +13703,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -13723,21 +13723,21 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I243" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13778,21 +13778,21 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -13813,17 +13813,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -13833,21 +13833,21 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -13868,17 +13868,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13888,21 +13888,21 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -13923,12 +13923,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -13943,25 +13943,25 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -13978,17 +13978,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -13998,25 +13998,25 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14053,25 +14053,25 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14108,25 +14108,25 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -14143,12 +14143,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -14168,16 +14168,16 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -14198,17 +14198,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14223,16 +14223,16 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -14253,12 +14253,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -14273,21 +14273,21 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14308,17 +14308,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -14328,21 +14328,21 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14383,21 +14383,21 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -14418,17 +14418,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14438,21 +14438,21 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I256" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -14473,17 +14473,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14493,21 +14493,21 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -14548,25 +14548,25 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -14583,17 +14583,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -14603,25 +14603,25 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -14658,25 +14658,25 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I260" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14713,25 +14713,25 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -14748,12 +14748,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -14773,16 +14773,16 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I262" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -14803,17 +14803,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -14828,16 +14828,16 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I263" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -14858,12 +14858,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -14878,21 +14878,21 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I264" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14913,17 +14913,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -14933,21 +14933,21 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I265" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14988,21 +14988,21 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -15023,17 +15023,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15043,21 +15043,21 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I267" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -15078,17 +15078,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15098,21 +15098,21 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I268" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15133,12 +15133,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -15153,25 +15153,25 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I269" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -15208,25 +15208,25 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I270" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15263,25 +15263,25 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I271" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15318,25 +15318,25 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I272" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -15378,16 +15378,16 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I273" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -15408,17 +15408,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15433,16 +15433,16 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I274" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -15483,21 +15483,21 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15518,17 +15518,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -15538,21 +15538,21 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15593,21 +15593,21 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I277" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -15628,17 +15628,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15648,21 +15648,21 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I278" t="n">
-        <v>59</v>
+        <v>-29</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -15683,17 +15683,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -15703,21 +15703,21 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
           <t>2026/05/25</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I279" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -15738,12 +15738,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -15758,25 +15758,25 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I280" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -15793,17 +15793,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -15813,25 +15813,25 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
       <c r="I281" t="n">
-        <v>-20</v>
+        <v>62</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -15868,25 +15868,25 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I282" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -15923,25 +15923,25 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I283" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -15958,12 +15958,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -15983,16 +15983,16 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I284" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -16013,17 +16013,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16038,16 +16038,16 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I285" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -16102,7 +16102,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>-28</v>
+        <v>59</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -16143,21 +16143,21 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I287" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -16308,21 +16308,21 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I290" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16398,12 +16398,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -16423,16 +16423,16 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I292" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -16453,12 +16453,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -16478,20 +16478,20 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I293" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16563,17 +16563,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16588,25 +16588,25 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I295" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16618,17 +16618,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -16643,16 +16643,16 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16673,12 +16673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -16698,16 +16698,16 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I297" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -16728,12 +16728,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -16753,20 +16753,20 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I298" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16838,17 +16838,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16863,25 +16863,25 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I300" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16893,17 +16893,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16918,16 +16918,16 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -16948,12 +16948,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -16973,16 +16973,16 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -17028,20 +17028,20 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I303" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17138,12 +17138,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I305" t="n">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17193,12 +17193,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I306" t="n">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17273,27 +17273,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -17303,52 +17303,52 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I308" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -17358,25 +17358,25 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -17921,12 +17921,12 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -18018,23 +18018,133 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
+      <c r="I321" t="n">
+        <v>13</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I322" t="n">
+        <v>13</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
         <is>
           <t>2026/07/13</t>
         </is>
       </c>
-      <c r="I321" t="n">
+      <c r="I323" t="n">
         <v>5</v>
       </c>
-      <c r="J321" t="inlineStr">
+      <c r="J323" t="inlineStr">
         <is>
           <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="K323" t="inlineStr">
         <is>
           <t>2026/06/26 13:22:28</t>
         </is>

--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K323"/>
+  <dimension ref="A1:K325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7318,17 +7318,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>N1x 80W</t>
+          <t>RMB 100 25W</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7338,35 +7338,35 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>林晉弘</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
+          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026/07/10 08:18:13</t>
+          <t>2026/07/16 14:20:24</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Prestige N16 Flip Spark</t>
+          <t>Prestige N16 Spark</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7428,17 +7428,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7448,35 +7448,35 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026/06/16 08:16:09</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026/06/16 08:19:44</t>
+          <t>2026/06/16 08:16:09</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026/06/16 08:22:24</t>
+          <t>2026/06/16 08:19:44</t>
         </is>
       </c>
     </row>
@@ -7623,16 +7623,16 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>2026/10/26</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>-42</v>
+        <v>42</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026/06/16 08:28:05</t>
+          <t>2026/06/16 08:22:24</t>
         </is>
       </c>
     </row>
@@ -7678,16 +7678,16 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>42</v>
+        <v>-42</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7696,29 +7696,29 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026/06/16 08:33:57</t>
+          <t>2026/06/16 08:28:05</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7728,30 +7728,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:33:57</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8363,55 +8363,55 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8448,16 +8448,16 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -8478,17 +8478,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8558,16 +8558,16 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -8588,17 +8588,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8613,16 +8613,16 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8668,16 +8668,16 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -8698,17 +8698,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8778,16 +8778,16 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8808,17 +8808,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8833,16 +8833,16 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8888,16 +8888,16 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8918,17 +8918,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8998,16 +8998,16 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9053,16 +9053,16 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9108,16 +9108,16 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -9138,17 +9138,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9218,16 +9218,16 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -9248,17 +9248,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9273,16 +9273,16 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9328,16 +9328,16 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -9358,17 +9358,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9438,16 +9438,16 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -9468,17 +9468,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9493,16 +9493,16 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9548,16 +9548,16 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -9578,17 +9578,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
+          <t>2026/03/06</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>2026/03/13</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9658,16 +9658,16 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
+          <t>2026/03/21</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
           <t>2026/03/13</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>2026/03/21</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9708,30 +9708,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -9773,15 +9773,15 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>23</v>
+        <v>-12</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -9798,17 +9798,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>-15</v>
+        <v>23</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9853,17 +9853,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9878,16 +9878,16 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>8</v>
+        <v>-15</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9983,30 +9983,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10048,15 +10048,15 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>23</v>
+        <v>-12</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10073,17 +10073,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10098,16 +10098,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
+          <t>2026/02/26</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>-15</v>
+        <v>23</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -10128,17 +10128,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10153,16 +10153,16 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8</v>
+        <v>-15</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10233,12 +10233,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10248,40 +10248,40 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>-12</v>
+        <v>8</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -10336,24 +10336,24 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10363,35 +10363,35 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -10538,80 +10538,80 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
+          <t>2026/06/09</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
           <t>2026/06/19</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>2026/06/18</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026/06/22 16:04:37</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>263</v>
+        <v>-1</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/22 16:04:37</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11223,55 +11223,55 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11338,17 +11338,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11358,25 +11358,25 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11448,12 +11448,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11468,30 +11468,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11578,25 +11578,25 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11688,30 +11688,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11778,17 +11778,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11798,25 +11798,25 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11908,30 +11908,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11998,17 +11998,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12018,25 +12018,25 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -12128,30 +12128,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12218,17 +12218,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12238,25 +12238,25 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -12348,30 +12348,30 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>-352</v>
+        <v>59</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12438,17 +12438,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -12458,25 +12458,25 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
           <t>2026/03/31</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>2026/05/29</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>59</v>
+        <v>-352</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -12543,55 +12543,55 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
+          <t>2026/03/31</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
           <t>2026/05/29</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -12683,16 +12683,16 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -12743,11 +12743,11 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -12788,21 +12788,21 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -12823,12 +12823,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -12843,25 +12843,25 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -12878,45 +12878,45 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>8</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I228" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12953,25 +12953,25 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13043,17 +13043,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13068,16 +13068,16 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -13173,21 +13173,21 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13288,16 +13288,16 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13318,17 +13318,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13348,11 +13348,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -13393,21 +13393,21 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I237" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -13448,25 +13448,25 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I238" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -13483,45 +13483,45 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>8</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I239" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13558,25 +13558,25 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13673,16 +13673,16 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I242" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -13778,21 +13778,21 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I244" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -13893,16 +13893,16 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -13923,17 +13923,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -13953,11 +13953,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I247" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -13998,21 +13998,21 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -14033,12 +14033,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14053,25 +14053,25 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -14088,45 +14088,45 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>8</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I250" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14163,25 +14163,25 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I251" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14253,17 +14253,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14278,16 +14278,16 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -14363,12 +14363,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -14383,21 +14383,21 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -14498,16 +14498,16 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -14528,17 +14528,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -14558,11 +14558,11 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -14603,21 +14603,21 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I259" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -14638,12 +14638,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14658,25 +14658,25 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I260" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -14693,45 +14693,45 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>8</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I261" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14768,25 +14768,25 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I262" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -14858,17 +14858,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14883,16 +14883,16 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I264" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -14988,21 +14988,21 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15103,16 +15103,16 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I268" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15133,17 +15133,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -15163,11 +15163,11 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -15208,21 +15208,21 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I270" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -15243,12 +15243,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -15263,25 +15263,25 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -15298,45 +15298,45 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>8</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I272" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15373,25 +15373,25 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I273" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -15463,17 +15463,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15488,16 +15488,16 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I275" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -15573,12 +15573,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -15593,21 +15593,21 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>-29</v>
+        <v>59</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -15708,16 +15708,16 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
+          <t>2026/05/29</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
       <c r="I279" t="n">
-        <v>25</v>
+        <v>-29</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -15738,17 +15738,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -15768,11 +15768,11 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -15813,21 +15813,21 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -15848,12 +15848,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -15868,25 +15868,25 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -15903,45 +15903,45 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>8</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
           <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="I283" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15978,25 +15978,25 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>2026/04/30</t>
-        </is>
-      </c>
       <c r="I284" t="n">
-        <v>-67</v>
+        <v>-20</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -16068,17 +16068,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -16093,16 +16093,16 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
           <t>2026/04/30</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I286" t="n">
-        <v>59</v>
+        <v>-67</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>-28</v>
+        <v>59</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16233,17 +16233,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -16253,21 +16253,21 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I289" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -16288,17 +16288,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -16308,21 +16308,21 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>2026/06/28</t>
-        </is>
-      </c>
       <c r="I290" t="n">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16343,17 +16343,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -16363,21 +16363,21 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I291" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -16463,7 +16463,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -16508,17 +16508,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -16533,16 +16533,16 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I294" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -16673,17 +16673,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -16698,16 +16698,16 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I297" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -16783,17 +16783,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16808,16 +16808,16 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16973,16 +16973,16 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17058,17 +17058,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17083,16 +17083,16 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17248,12 +17248,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I307" t="n">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17278,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -17383,27 +17383,27 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -17413,25 +17413,25 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I310" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -17541,7 +17541,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -17976,12 +17976,12 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -18091,7 +18091,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -18128,25 +18128,135 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
+      <c r="I323" t="n">
+        <v>13</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
         <is>
           <t>2026/07/13</t>
         </is>
       </c>
-      <c r="I323" t="n">
+      <c r="I324" t="n">
         <v>5</v>
       </c>
-      <c r="J323" t="inlineStr">
+      <c r="J324" t="inlineStr">
         <is>
           <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="K324" t="inlineStr">
         <is>
           <t>2026/06/26 13:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>RMB 100 28W</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026/07/15</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>5</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2026/07/16 14:20:24</t>
         </is>
       </c>
     </row>

--- a/MP变动记录.xlsx
+++ b/MP变动记录.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K325"/>
+  <dimension ref="A1:K329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2648,330 +2648,330 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17U1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VenturePro 17 AI A2HVEG</t>
+          <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025/07/12</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2025/04/15</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>-88</v>
+        <v>5</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/19),後續將依實際測試結果滾動式調整專案時程。  2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/07/17 11:04:53</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17U1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VenturePro 17 AI A2HVEG</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2025/07/12</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025/04/15</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>-88</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/19),後續將依實際測試結果滾動式調整專案時程。  2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/07/17 11:04:53</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/19),後續將依實際測試結果滾動式調整專案時程。  2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/07/17 11:04:53</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/19),後續將依實際測試結果滾動式調整專案時程。  2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/07/17 11:04:53</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>17U1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>VenturePro 17 AI A2HVEG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2025/07/12</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>-2</v>
+        <v>-88</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>17U1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>VenturePro 17 AI A2HVEG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2025/07/12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>-2</v>
+        <v>-88</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4401,89 +4401,89 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>BTO未開</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4493,37 +4493,42 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14</v>
+        <v>-2</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4533,7 +4538,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4543,75 +4548,80 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>BTO未開</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>182L</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WIG</t>
+          <t>Titan 18 HX Dragon Edition Draco Epic A2WJ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>許婕</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2025/02/28</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025/03/14</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>14</v>
+        <v>-2</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4676,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4726,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4781,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4831,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4886,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4936,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4991,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5041,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5053,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Raider A18 HX A9WIG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5063,12 +5073,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5077,16 +5087,16 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>-26</v>
+        <v>-14</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>業務8/6通知開BTO</t>
+          <t>BTO未開</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -5098,17 +5108,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Raider A18 HX A9WJG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5123,20 +5133,20 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2025/03/17</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025/03/26</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5158,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vector A18 HX A9WHG</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5168,25 +5178,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2025/04/02</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025/03/27</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>-6</v>
+        <v>-14</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>BTO未開</t>
+        </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5251,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5306,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5356,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5406,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -5441,227 +5456,212 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM</t>
+          <t>Raider A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2025/03/26</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>-26</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>業務8/6通知開BTO</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
+          <t>Raider A18 HX A9WJG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/03/17</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/26</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>follow 12XE</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM</t>
+          <t>Vector A18 HX A9WHG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2025/04/02</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/27</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
-        </is>
+        <v>-6</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1T91</t>
+          <t>182L</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
+          <t>Vector A18 HX A9WIG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PTL-H 25W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2025/02/28</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2025/03/14</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>follow 12XE</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -6541,24 +6541,24 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6568,52 +6568,52 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6623,52 +6623,52 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>follow 12XE</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6678,52 +6678,52 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) Schedule: ATS搖桿燈光異常Issue的實驗影響4 days 2)中國區出貨：目前影響訂單為 520(May)台a.3C認證預計6/18 ready(因測試fail)需要pull in 到6/B,b.SRRC認證:可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) . SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Claw 8 EX AI+ CG3EM Launch Pack</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6733,35 +6733,35 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>follow 12XE</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -7196,12 +7196,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -7251,12 +7251,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -7293,25 +7293,25 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）  3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026/06/18 13:35:09</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RMB 100 25W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7343,47 +7343,47 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026/07/16 14:20:24</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>N1x 80W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>林晉弘</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7403,42 +7403,42 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026/07/10 08:18:13</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Prestige N16 Flip Spark</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>N1x 80W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>林晉弘</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7458,42 +7458,42 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/06/25</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026/07/10 08:18:13</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 35W</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7503,52 +7503,52 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）  3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026/06/16 08:16:09</t>
+          <t>2026/06/18 13:35:09</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RMB 100 25W</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7558,52 +7558,52 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026/06/16 08:19:44</t>
+          <t>2026/07/16 14:20:24</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Prestige N16 Spark</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7613,52 +7613,52 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026/06/16 08:22:24</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
+          <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7668,35 +7668,35 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>EVT</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>-42</v>
+        <v>17</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。  3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證 4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026/06/16 08:28:05</t>
+          <t>2026/07/10 08:18:13</t>
         </is>
       </c>
     </row>
@@ -7751,29 +7751,29 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026/06/16 08:33:57</t>
+          <t>2026/06/16 08:16:09</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7783,52 +7783,52 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:19:44</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7838,52 +7838,52 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:22:24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7893,52 +7893,52 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>-42</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:28:05</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7948,30 +7948,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/16 08:33:57</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -8411,227 +8411,227 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -9743,17 +9743,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9763,30 +9763,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -9883,11 +9883,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026/03/06</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -9983,25 +9983,25 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WH</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10048,20 +10048,20 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>-12</v>
+        <v>23</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>follow RTX5090，BTO暫無需求</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -10073,17 +10073,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WI</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10098,16 +10098,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>23</v>
+        <v>-15</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -10128,17 +10128,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B2WJ</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ARL-HX 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10153,16 +10153,16 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
+          <t>2026/03/13</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
           <t>2026/03/21</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>2026/03/06</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>-15</v>
+        <v>8</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WH</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Raider 16  HX B2WI</t>
+          <t>Raider 16 Max HX B2WH</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10258,25 +10258,25 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026/03/13</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026/03/21</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>8</v>
+        <v>-12</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>follow RTX5090，BTO暫無需求</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10288,12 +10288,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16 Max HX B2WI</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10323,70 +10323,70 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>-12</v>
+        <v>23</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Raider 16 HX B2WF</t>
+          <t>Raider 16 Max HX B2WJ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ARL-HX refresh 55W</t>
+          <t>ARL-HX 55W</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>BTO-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026/02/14</t>
+          <t>2026/03/06</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10398,127 +10398,127 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16  HX B2WH</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16  HX B2WI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/03/13</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/03/21</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10528,52 +10528,52 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026/06/09</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Raider 16 HX B2WF</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>ARL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10583,255 +10583,255 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>BTO-</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/02/26</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/02/14</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
+          <t>SKU目前沒有訂單.可以follow RTX5060 ATS做ATS CR</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026/06/22 16:04:37</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/09</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>263</v>
+        <v>10</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19  2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/06/19</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>263</v>
+        <v>-1</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/06/22 16:04:37</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -11271,24 +11271,24 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WH</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11298,52 +11298,52 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Raider A16 HX B8WI</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11353,52 +11353,52 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
+          <t>2026/06/28</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2026/03/31</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>-352</v>
+        <v>263</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11408,90 +11408,90 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>265K</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Raider A16 HX B9WH</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>梅燕</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026/03/31</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>無業務報價，MVT on hold</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -12591,19 +12591,19 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Raider A16 HX B8WH</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12613,52 +12613,52 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>-29</v>
+        <v>-352</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Raider A16 HX B8WI</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12668,12 +12668,12 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12683,107 +12683,107 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>-29</v>
+        <v>-352</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SRRC未pass 1) 可以清關入中國區,但是上架販售有風險(需要有SRRC 認證) , 目前影響訂單為600 pcs 2) SRRC目前狀況,等釋放名額,安排實驗室後才有schedule.請安規team 協助update</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>265K</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Raider A16 HX B9WH</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>梅燕</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/03/31</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="I226" t="n">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>無業務報價，MVT on hold</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2026/05/28 16:45:33</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -12823,12 +12823,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -12843,21 +12843,21 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -12898,25 +12898,25 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12953,25 +12953,25 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I229" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -12988,12 +12988,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -13013,16 +13013,16 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I230" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -13043,17 +13043,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13063,21 +13063,21 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -13098,12 +13098,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -13118,25 +13118,25 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I232" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -13153,17 +13153,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13173,25 +13173,25 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I233" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13283,12 +13283,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13318,17 +13318,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13348,11 +13348,11 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I236" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13373,12 +13373,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2026/05/28 16:56:28</t>
+          <t>2026/05/28 16:45:33</t>
         </is>
       </c>
     </row>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -13448,21 +13448,21 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I238" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -13503,25 +13503,25 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I239" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13558,25 +13558,25 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I240" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -13618,16 +13618,16 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I241" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -13668,21 +13668,21 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I242" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -13723,25 +13723,25 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I243" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -13778,25 +13778,25 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I244" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -13902,7 +13902,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13923,17 +13923,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -13943,7 +13943,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -13953,11 +13953,11 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I247" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -13978,12 +13978,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026/05/28 17:13:54</t>
+          <t>2026/05/28 16:56:28</t>
         </is>
       </c>
     </row>
@@ -14033,12 +14033,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -14053,21 +14053,21 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14098,7 +14098,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14108,25 +14108,25 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I250" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -14163,25 +14163,25 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -14198,12 +14198,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -14223,16 +14223,16 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I252" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -14253,17 +14253,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14273,21 +14273,21 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I253" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -14308,12 +14308,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -14328,25 +14328,25 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I254" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -14363,17 +14363,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -14383,25 +14383,25 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -14452,7 +14452,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14473,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -14493,12 +14493,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14528,17 +14528,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -14558,11 +14558,11 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I258" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14583,12 +14583,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2026/05/28 17:17:28</t>
+          <t>2026/05/28 17:13:54</t>
         </is>
       </c>
     </row>
@@ -14638,12 +14638,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14658,21 +14658,21 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I260" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -14713,25 +14713,25 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I261" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -14768,25 +14768,25 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -14828,16 +14828,16 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I263" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -14858,17 +14858,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -14878,21 +14878,21 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I264" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -14933,25 +14933,25 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I265" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -14968,17 +14968,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -14988,25 +14988,25 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I266" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15098,12 +15098,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -15112,7 +15112,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -15133,17 +15133,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -15163,11 +15163,11 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I269" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15188,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>2026/05/28 17:21:14</t>
+          <t>2026/05/28 17:17:28</t>
         </is>
       </c>
     </row>
@@ -15243,12 +15243,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -15263,21 +15263,21 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I271" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -15318,25 +15318,25 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I272" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -15373,25 +15373,25 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I273" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -15408,12 +15408,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -15433,16 +15433,16 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I274" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -15463,17 +15463,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -15483,21 +15483,21 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I275" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -15518,12 +15518,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -15538,25 +15538,25 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -15573,17 +15573,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -15593,25 +15593,25 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -15648,12 +15648,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>ATS-</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -15703,12 +15703,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026/05/29</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>-29</v>
+        <v>-67</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15738,17 +15738,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E8WGXK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -15768,11 +15768,11 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15793,12 +15793,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>2026/05/28 17:24:17</t>
+          <t>2026/05/28 17:21:14</t>
         </is>
       </c>
     </row>
@@ -15848,12 +15848,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E8WEK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -15868,21 +15868,21 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS-</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026/05/25</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>62</v>
+        <v>-29</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E8WFK</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -15923,25 +15923,25 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/05/29</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I283" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E8WGXK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15978,25 +15978,25 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="I284" t="n">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -16038,16 +16038,16 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I285" t="n">
-        <v>-67</v>
+        <v>59</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -16068,17 +16068,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E8WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -16088,21 +16088,21 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/05/25</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I286" t="n">
-        <v>-67</v>
+        <v>62</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -16143,25 +16143,25 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I287" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -16178,17 +16178,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Crosshair A16 Max HX E9WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -16198,25 +16198,25 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="I288" t="n">
-        <v>59</v>
+        <v>-20</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/6前完成；2) Packing: 為不影響TTM,WW版本需提供包材測試before 6/10</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -16233,12 +16233,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E8WEK</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -16258,16 +16258,16 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I289" t="n">
-        <v>-28</v>
+        <v>-67</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16288,12 +16288,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E8WFK</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -16308,21 +16308,21 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="I290" t="n">
-        <v>28</v>
+        <v>-67</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2026/06/08 16:58:53</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>-28</v>
+        <v>59</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 Max HX E9WEK</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -16418,21 +16418,21 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
+          <t>2026/04/30</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I292" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2026/06/08 17:01:57</t>
+          <t>2026/05/28 17:24:17</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -16473,21 +16473,21 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
           <t>2026/06/28</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
       <c r="I293" t="n">
-        <v>28</v>
+        <v>-28</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 16:58:53</t>
         </is>
       </c>
     </row>
@@ -16563,12 +16563,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -16583,21 +16583,21 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="I295" t="n">
-        <v>2</v>
+        <v>-28</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16618,12 +16618,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -16643,25 +16643,25 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/06/08 17:01:57</t>
         </is>
       </c>
     </row>
@@ -16673,17 +16673,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -16698,16 +16698,16 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I297" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16783,17 +16783,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -16808,16 +16808,16 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16876,12 +16876,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -16931,12 +16931,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/06/15 13:44:06</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16973,16 +16973,16 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -17058,17 +17058,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17083,16 +17083,16 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026/06/28</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/06/15 13:47:47</t>
         </is>
       </c>
     </row>
@@ -17223,17 +17223,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17248,16 +17248,16 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I307" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -17278,17 +17278,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -17303,16 +17303,16 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/06/28</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="I308" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17358,12 +17358,12 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I309" t="n">
@@ -17371,12 +17371,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I310" t="n">
@@ -17426,39 +17426,39 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中; 3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -17477,43 +17477,43 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2026/05/28 14:07:11</t>
+          <t>2026/06/15 13:49:36</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -17523,52 +17523,52 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I312" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2026/05/28 14:17:44</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -17578,52 +17578,52 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；2) Packing: WW版本設計確認中;3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2026/05/28 14:27:19</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -17633,25 +17633,25 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="I314" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2026/05/28 14:42:30</t>
+          <t>2026/06/26 13:22:28</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2026/05/28 14:54:18</t>
+          <t>2026/05/28 14:07:11</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2026/05/28 15:00:33</t>
+          <t>2026/05/28 14:17:44</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2026/05/28 15:12:31</t>
+          <t>2026/05/28 14:27:19</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2026/05/28 15:22:48</t>
+          <t>2026/05/28 14:42:30</t>
         </is>
       </c>
     </row>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2026/05/28 15:30:50</t>
+          <t>2026/05/28 14:54:18</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2026/05/28 15:36:04</t>
+          <t>2026/05/28 15:00:33</t>
         </is>
       </c>
     </row>
@@ -18031,12 +18031,12 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2026/06/15 13:44:06</t>
+          <t>2026/05/28 15:12:31</t>
         </is>
       </c>
     </row>
@@ -18086,12 +18086,12 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>2026/06/15 13:47:47</t>
+          <t>2026/05/28 15:22:48</t>
         </is>
       </c>
     </row>
@@ -18141,12 +18141,12 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>2026/06/15 13:49:36</t>
+          <t>2026/05/28 15:30:50</t>
         </is>
       </c>
     </row>
@@ -18183,25 +18183,25 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>2026/07/13</t>
-        </is>
-      </c>
       <c r="I324" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
+          <t>1)物料 WLAN：5/28 ETA* 10K ,   Adapter ：目標6K， 需pull-in到06/15  ETA 2)認證  CE 06/06 ready ，PH  NTC 認證：需reddot 客戶協助CE Ready+3W 拿證，預計6/E 只能滿足PH地區出貨，EU：TUV 認證预计7/E ，其他地區認證follow  In house 流程，有訂單需求後由業務通知申請 3)TYPEC+USB4接口 SI测试Fail，需主板升级，微步確認評估預計最快7/8 TTM，已同步請微步内部評估和供应商沟通，按6月底的目标推进，待微步確認回復，Schedule TBD</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>2026/06/26 13:22:28</t>
+          <t>2026/05/28 15:36:04</t>
         </is>
       </c>
     </row>
@@ -18218,43 +18218,263 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I325" t="n">
+        <v>13</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I326" t="n">
+        <v>13</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:47:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="I327" t="n">
+        <v>13</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步 2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復） 3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA， 4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2026/06/15 13:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>2026/07/13</t>
+        </is>
+      </c>
+      <c r="I328" t="n">
+        <v>5</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>2026/06/26 13:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
           <t>RMB 100 28W</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
+      <c r="E329" t="inlineStr">
         <is>
           <t>杜晨光</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
+      <c r="F329" t="inlineStr">
         <is>
           <t>ATS</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
+      <c r="H329" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="I325" t="n">
+      <c r="I329" t="n">
         <v>5</v>
       </c>
-      <c r="J325" t="inlineStr">
+      <c r="J329" t="inlineStr">
         <is>
           <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K329" t="inlineStr">
         <is>
           <t>2026/07/16 14:20:24</t>
         </is>
